--- a/design_tables/excel/Enum.xlsx
+++ b/design_tables/excel/Enum.xlsx
@@ -68,117 +68,6 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EffectTypeTable" displayName="EffectTypeTable" ref="A1:D7" headerRowCount="1">
-  <x:tableColumns count="4">
-    <x:tableColumn id="1" name="value"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="value_format"/>
-    <x:tableColumn id="4" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="ValueDamageTypeTable" displayName="ValueDamageTypeTable" ref="A1:C7" headerRowCount="1">
-  <x:tableColumns count="3">
-    <x:tableColumn id="1" name="value"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TargetTypeTable" displayName="TargetTypeTable" ref="A1:C7" headerRowCount="1">
-  <x:tableColumns count="3">
-    <x:tableColumn id="1" name="value"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TargetSourceTable" displayName="TargetSourceTable" ref="A1:C9" headerRowCount="1">
-  <x:tableColumns count="3">
-    <x:tableColumn id="1" name="value"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TriggerTimingTable" displayName="TriggerTimingTable" ref="A1:C14" headerRowCount="1">
-  <x:tableColumns count="3">
-    <x:tableColumn id="1" name="value"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DurationTypeTable" displayName="DurationTypeTable" ref="A1:C8" headerRowCount="1">
-  <x:tableColumns count="3">
-    <x:tableColumn id="1" name="value"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="DurationApplyPolicyTable" displayName="DurationApplyPolicyTable" ref="A1:C6" headerRowCount="1">
-  <x:tableColumns count="3">
-    <x:tableColumn id="1" name="value"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="ExpirePolicyTable" displayName="ExpirePolicyTable" ref="A1:C6" headerRowCount="1">
-  <x:tableColumns count="3">
-    <x:tableColumn id="1" name="value"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="OnRemoveTable" displayName="OnRemoveTable" ref="A1:C4" headerRowCount="1">
-  <x:tableColumns count="3">
-    <x:tableColumn id="1" name="value"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="ValueResourceTypeTable" displayName="ValueResourceTypeTable" ref="A1:C9" headerRowCount="1">
-  <x:tableColumns count="3">
-    <x:tableColumn id="1" name="value"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -434,9 +323,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R693fcf3072804796"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
 
